--- a/12626455.xlsx
+++ b/12626455.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D597F80F-B1FD-4E68-BDDE-CEBD8B972B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417FE8C7-4480-4470-8FC7-D234CC1EB527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,42 @@
   </si>
   <si>
     <t>Feeling low in morning but by evening energy came back.</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Feeling low by end of day.</t>
+  </si>
+  <si>
+    <t>Good day</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Okaish</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>At home.</t>
+  </si>
+  <si>
+    <t>Got fever</t>
+  </si>
+  <si>
+    <t>Rest due to fever</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Left home</t>
   </si>
 </sst>
 </file>
@@ -1145,161 +1181,279 @@
       <c r="A9" s="13">
         <v>46259</v>
       </c>
-      <c r="B9" s="14"/>
+      <c r="B9" s="14">
+        <v>360</v>
+      </c>
       <c r="C9" s="14">
         <v>30</v>
       </c>
       <c r="D9" s="14">
-        <v>360</v>
-      </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
+        <v>60</v>
+      </c>
+      <c r="E9" s="14">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14">
+        <v>300</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>100</v>
+      </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>390</v>
+        <v>880</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>1050</v>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
+      <c r="A10" s="13">
+        <v>46260</v>
+      </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="E10" s="14">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14">
+        <v>250</v>
+      </c>
+      <c r="G10" s="14">
+        <v>5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>150</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>400</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>1040</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
+      <c r="A11" s="13">
+        <v>46261</v>
+      </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="E11" s="14">
+        <v>45</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>405</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>1035</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
+      <c r="A12" s="13">
+        <v>46262</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+      <c r="E12" s="14">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
+        <v>0</v>
+      </c>
+      <c r="J12" s="15">
+        <v>0</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
+      <c r="A13" s="13">
+        <v>46263</v>
+      </c>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
+        <v>0</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
+      <c r="A14" s="13">
+        <v>46264</v>
+      </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
+        <v>0</v>
+      </c>
+      <c r="J14" s="15">
+        <v>0</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
+      <c r="A15" s="13">
+        <v>46265</v>
+      </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>

--- a/12626455.xlsx
+++ b/12626455.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417FE8C7-4480-4470-8FC7-D234CC1EB527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AAC0C6-E893-4552-A9D7-EDF55EB9FEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -258,7 +258,58 @@
     <t>Unsatisfied</t>
   </si>
   <si>
-    <t>Left home</t>
+    <t>Left my home</t>
+  </si>
+  <si>
+    <t>Started classes again, feel awkward</t>
+  </si>
+  <si>
+    <t>Python ca so some stress</t>
+  </si>
+  <si>
+    <t>Feeling tired 7 class were there</t>
+  </si>
+  <si>
+    <t>Feeling great</t>
+  </si>
+  <si>
+    <t>Networking ca, wrote down everything I know.</t>
+  </si>
+  <si>
+    <t>Feeling low</t>
+  </si>
+  <si>
+    <t>feeling unwell got fever</t>
+  </si>
+  <si>
+    <t>Tired as hell still on meds</t>
+  </si>
+  <si>
+    <t>Started feeling a bit well but still tired</t>
+  </si>
+  <si>
+    <t>Much better than before</t>
+  </si>
+  <si>
+    <t>Excellent start but mostly lying on bed</t>
+  </si>
+  <si>
+    <t>Awkward to go into classes after a weekend</t>
+  </si>
+  <si>
+    <t>Mostly slept</t>
+  </si>
+  <si>
+    <t>woke up more but did nothing</t>
+  </si>
+  <si>
+    <t>Tired after the classes</t>
+  </si>
+  <si>
+    <t>Feeling okaish</t>
+  </si>
+  <si>
+    <t>Feeling great less classes conducted</t>
   </si>
 </sst>
 </file>
@@ -370,7 +421,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -393,11 +444,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -441,6 +503,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -912,10 +977,11 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="33.81640625" customWidth="1"/>
-    <col min="5" max="6" width="11" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
@@ -1111,7 +1177,7 @@
         <v>130</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>655</v>
       </c>
       <c r="J7" s="15">
@@ -1455,379 +1521,685 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
+    <row r="16" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>46266</v>
+      </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
+        <v>960</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>46267</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+      <c r="E17" s="14">
+        <v>25</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>198</v>
+      </c>
+      <c r="I17" s="15">
+        <f>IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
+        <v>473</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>967</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
+      <c r="A18" s="13">
+        <v>46268</v>
+      </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="E18" s="14">
+        <v>43</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>134</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>477</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>963</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
+      <c r="A19" s="13">
+        <v>46269</v>
+      </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="E19" s="14">
+        <v>61</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>210</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>621</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>819</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
+      <c r="A20" s="13">
+        <v>46270</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="E20" s="14">
+        <v>40</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>120</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>160</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>1280</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
+      <c r="A21" s="13">
+        <v>46271</v>
+      </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="E21" s="14">
+        <v>80</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>167</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>247</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
+        <v>1193</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="13">
+        <v>46272</v>
+      </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="E22" s="14">
+        <v>65</v>
+      </c>
+      <c r="F22" s="14">
+        <v>150</v>
+      </c>
+      <c r="G22" s="14">
+        <v>3</v>
+      </c>
+      <c r="H22" s="14">
+        <v>188</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>403</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>1037</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
+      <c r="A23" s="13">
+        <v>46273</v>
+      </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>250</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>125</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>405</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>1035</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
+      <c r="A24" s="13">
+        <v>46274</v>
+      </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="E24" s="14">
+        <v>45</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>173</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>468</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>972</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
+      <c r="A25" s="13">
+        <v>46275</v>
+      </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+      <c r="E25" s="14">
+        <v>75</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>195</v>
+      </c>
+      <c r="I25" s="15">
+        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
+        <v>570</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
+        <v>870</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46276</v>
+      </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="E26" s="14">
+        <v>55</v>
+      </c>
+      <c r="F26" s="21">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>170</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>575</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>865</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
+      <c r="A27" s="13">
+        <v>46277</v>
+      </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="E27" s="14">
+        <v>95</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>172</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>267</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
+        <v>1173</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="13">
+        <v>46278</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="E28" s="14">
+        <v>110</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>174</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>284</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
+        <v>1156</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>46279</v>
+      </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>185</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>445</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>995</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
+      <c r="A30" s="13">
+        <v>46280</v>
+      </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="E30" s="14">
+        <v>35</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>127</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>362</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>1078</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
+      <c r="A31" s="13">
+        <v>46281</v>
+      </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="E31" s="14">
+        <v>40</v>
+      </c>
+      <c r="F31" s="14">
+        <v>200</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14">
+        <v>190</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>430</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>1010</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
+      <c r="A32" s="13">
+        <v>46282</v>
+      </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>350</v>
+      </c>
+      <c r="G32" s="14">
+        <v>7</v>
+      </c>
+      <c r="H32" s="14">
+        <v>193</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>603</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>837</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>

--- a/12626455.xlsx
+++ b/12626455.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0AAC0C6-E893-4552-A9D7-EDF55EB9FEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A469DF-7521-40B9-A340-4E8CE49E0DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -267,9 +267,6 @@
     <t>Python ca so some stress</t>
   </si>
   <si>
-    <t>Feeling tired 7 class were there</t>
-  </si>
-  <si>
     <t>Feeling great</t>
   </si>
   <si>
@@ -310,6 +307,15 @@
   </si>
   <si>
     <t>Feeling great less classes conducted</t>
+  </si>
+  <si>
+    <t>Feeling tired 6 class were there</t>
+  </si>
+  <si>
+    <t>Feeling tired becoz of 7 classes</t>
+  </si>
+  <si>
+    <t>Ca was there and Saturday ruined</t>
   </si>
 </sst>
 </file>
@@ -500,12 +506,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -977,11 +983,11 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.26953125" customWidth="1"/>
+    <col min="1" max="1" width="19.90625" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="33.81640625" customWidth="1"/>
     <col min="5" max="5" width="14.26953125" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
@@ -992,74 +998,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12626455</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1159,7 +1165,7 @@
         <v>420</v>
       </c>
       <c r="C7" s="14">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="D7" s="14">
         <v>60</v>
@@ -1174,15 +1180,15 @@
         <v>0</v>
       </c>
       <c r="H7" s="14">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="I7" s="15">
         <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>785</v>
+        <v>760</v>
       </c>
       <c r="K7" t="s">
         <v>49</v>
@@ -1205,7 +1211,7 @@
         <v>240</v>
       </c>
       <c r="C8" s="14">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D8" s="14">
         <v>0</v>
@@ -1220,15 +1226,15 @@
         <v>4</v>
       </c>
       <c r="H8" s="14">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>57</v>
@@ -1251,7 +1257,7 @@
         <v>360</v>
       </c>
       <c r="C9" s="14">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D9" s="14">
         <v>60</v>
@@ -1266,15 +1272,15 @@
         <v>6</v>
       </c>
       <c r="H9" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>910</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>62</v>
@@ -1293,9 +1299,15 @@
       <c r="A10" s="13">
         <v>46260</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
+      <c r="B10" s="14">
+        <v>300</v>
+      </c>
+      <c r="C10" s="14">
+        <v>150</v>
+      </c>
+      <c r="D10" s="14">
+        <v>30</v>
+      </c>
       <c r="E10" s="14">
         <v>0</v>
       </c>
@@ -1306,15 +1318,15 @@
         <v>5</v>
       </c>
       <c r="H10" s="14">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>1040</v>
+        <v>640</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
@@ -1333,9 +1345,15 @@
       <c r="A11" s="13">
         <v>46261</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
+      <c r="B11" s="14">
+        <v>390</v>
+      </c>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>40</v>
+      </c>
       <c r="E11" s="14">
         <v>45</v>
       </c>
@@ -1350,11 +1368,11 @@
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>405</v>
+        <v>895</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>545</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>65</v>
@@ -1373,9 +1391,15 @@
       <c r="A12" s="13">
         <v>46262</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="B12" s="14">
+        <v>120</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0</v>
+      </c>
       <c r="E12" s="14">
         <v>0</v>
       </c>
@@ -1386,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I12" s="15">
         <v>0</v>
@@ -1411,9 +1435,15 @@
       <c r="A13" s="13">
         <v>46263</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="B13" s="14">
+        <v>240</v>
+      </c>
+      <c r="C13" s="14">
+        <v>15</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
       <c r="E13" s="14">
         <v>0</v>
       </c>
@@ -1424,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="14">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I13" s="15">
         <v>0</v>
@@ -1449,9 +1479,15 @@
       <c r="A14" s="13">
         <v>46264</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
+      <c r="B14" s="14">
+        <v>300</v>
+      </c>
+      <c r="C14" s="14">
+        <v>15</v>
+      </c>
+      <c r="D14" s="14">
+        <v>0</v>
+      </c>
       <c r="E14" s="14">
         <v>0</v>
       </c>
@@ -1462,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I14" s="15">
         <v>0</v>
@@ -1487,9 +1523,15 @@
       <c r="A15" s="13">
         <v>46265</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
+      <c r="B15" s="14">
+        <v>360</v>
+      </c>
+      <c r="C15" s="14">
+        <v>45</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0</v>
+      </c>
       <c r="E15" s="14">
         <v>0</v>
       </c>
@@ -1500,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I15" s="15">
         <v>0</v>
@@ -1525,9 +1567,15 @@
       <c r="A16" s="13">
         <v>46266</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="B16" s="14">
+        <v>120</v>
+      </c>
+      <c r="C16" s="14">
+        <v>120</v>
+      </c>
+      <c r="D16" s="14">
+        <v>15</v>
+      </c>
       <c r="E16" s="14">
         <v>60</v>
       </c>
@@ -1542,11 +1590,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>735</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>705</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>49</v>
@@ -1565,9 +1613,15 @@
       <c r="A17" s="13">
         <v>46267</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="B17" s="14">
+        <v>300</v>
+      </c>
+      <c r="C17" s="14">
+        <v>198</v>
+      </c>
+      <c r="D17" s="14">
+        <v>30</v>
+      </c>
       <c r="E17" s="14">
         <v>25</v>
       </c>
@@ -1578,15 +1632,15 @@
         <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="I17" s="15">
         <f>IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
-        <v>473</v>
+        <v>838</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>967</v>
+        <v>602</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
@@ -1598,16 +1652,22 @@
         <v>51</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
         <v>46268</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>134</v>
+      </c>
+      <c r="D18" s="14">
+        <v>45</v>
+      </c>
       <c r="E18" s="14">
         <v>43</v>
       </c>
@@ -1618,15 +1678,15 @@
         <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>477</v>
+        <v>1069</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>963</v>
+        <v>371</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>67</v>
@@ -1638,16 +1698,22 @@
         <v>59</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">
         <v>46269</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>210</v>
+      </c>
+      <c r="D19" s="14">
+        <v>25</v>
+      </c>
       <c r="E19" s="14">
         <v>61</v>
       </c>
@@ -1658,15 +1724,15 @@
         <v>7</v>
       </c>
       <c r="H19" s="14">
-        <v>210</v>
+        <v>55</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>621</v>
+        <v>1121</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>819</v>
+        <v>319</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>62</v>
@@ -1678,16 +1744,22 @@
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
         <v>46270</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
+      <c r="B20" s="14">
+        <v>360</v>
+      </c>
+      <c r="C20" s="14">
+        <v>120</v>
+      </c>
+      <c r="D20" s="14">
+        <v>15</v>
+      </c>
       <c r="E20" s="14">
         <v>40</v>
       </c>
@@ -1698,15 +1770,15 @@
         <v>0</v>
       </c>
       <c r="H20" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>160</v>
+        <v>625</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>1280</v>
+        <v>815</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>57</v>
@@ -1718,16 +1790,22 @@
         <v>57</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
         <v>46271</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14">
+        <v>167</v>
+      </c>
+      <c r="D21" s="14">
+        <v>55</v>
+      </c>
       <c r="E21" s="14">
         <v>80</v>
       </c>
@@ -1738,15 +1816,15 @@
         <v>0</v>
       </c>
       <c r="H21" s="14">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>247</v>
+        <v>707</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>1193</v>
+        <v>733</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>57</v>
@@ -1758,16 +1836,22 @@
         <v>57</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
         <v>46272</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
+      <c r="B22" s="14">
+        <v>300</v>
+      </c>
+      <c r="C22" s="14">
+        <v>188</v>
+      </c>
+      <c r="D22" s="14">
+        <v>35</v>
+      </c>
       <c r="E22" s="14">
         <v>65</v>
       </c>
@@ -1778,15 +1862,15 @@
         <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>403</v>
+        <v>748</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>1037</v>
+        <v>692</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>65</v>
@@ -1798,16 +1882,22 @@
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13">
         <v>46273</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>125</v>
+      </c>
+      <c r="D23" s="14">
+        <v>25</v>
+      </c>
       <c r="E23" s="14">
         <v>30</v>
       </c>
@@ -1818,15 +1908,15 @@
         <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>405</v>
+        <v>880</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>1035</v>
+        <v>560</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1838,16 +1928,22 @@
         <v>57</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
         <v>46274</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>173</v>
+      </c>
+      <c r="D24" s="14">
+        <v>15</v>
+      </c>
       <c r="E24" s="14">
         <v>45</v>
       </c>
@@ -1858,15 +1954,15 @@
         <v>5</v>
       </c>
       <c r="H24" s="14">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>468</v>
+        <v>958</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>972</v>
+        <v>482</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>49</v>
@@ -1878,16 +1974,22 @@
         <v>51</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13">
         <v>46275</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
+      <c r="B25" s="14">
+        <v>540</v>
+      </c>
+      <c r="C25" s="14">
+        <v>195</v>
+      </c>
+      <c r="D25" s="14">
+        <v>35</v>
+      </c>
       <c r="E25" s="14">
         <v>75</v>
       </c>
@@ -1898,15 +2000,15 @@
         <v>6</v>
       </c>
       <c r="H25" s="14">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="I25" s="15">
         <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
-        <v>570</v>
+        <v>1165</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>870</v>
+        <v>275</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>65</v>
@@ -1918,35 +2020,41 @@
         <v>57</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
         <v>46276</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
+      <c r="B26" s="14">
+        <v>510</v>
+      </c>
+      <c r="C26" s="14">
+        <v>170</v>
+      </c>
+      <c r="D26" s="14">
+        <v>30</v>
+      </c>
       <c r="E26" s="14">
         <v>55</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="18">
         <v>350</v>
       </c>
       <c r="G26" s="14">
         <v>7</v>
       </c>
       <c r="H26" s="14">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>575</v>
+        <v>1195</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>865</v>
+        <v>245</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>62</v>
@@ -1958,16 +2066,22 @@
         <v>59</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">
         <v>46277</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>172</v>
+      </c>
+      <c r="D27" s="14">
+        <v>65</v>
+      </c>
       <c r="E27" s="14">
         <v>95</v>
       </c>
@@ -1978,15 +2092,15 @@
         <v>0</v>
       </c>
       <c r="H27" s="14">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>267</v>
+        <v>872</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>1173</v>
+        <v>568</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>67</v>
@@ -1998,16 +2112,22 @@
         <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
         <v>46278</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>174</v>
+      </c>
+      <c r="D28" s="14">
+        <v>10</v>
+      </c>
       <c r="E28" s="14">
         <v>110</v>
       </c>
@@ -2018,15 +2138,15 @@
         <v>0</v>
       </c>
       <c r="H28" s="14">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>284</v>
+        <v>724</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>1156</v>
+        <v>716</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>67</v>
@@ -2038,16 +2158,22 @@
         <v>57</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
         <v>46279</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
+      <c r="B29" s="14">
+        <v>300</v>
+      </c>
+      <c r="C29" s="14">
+        <v>185</v>
+      </c>
+      <c r="D29" s="14">
+        <v>20</v>
+      </c>
       <c r="E29" s="14">
         <v>60</v>
       </c>
@@ -2062,11 +2188,11 @@
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>445</v>
+        <v>950</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>995</v>
+        <v>490</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>
@@ -2078,16 +2204,22 @@
         <v>59</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
         <v>46280</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
+      <c r="B30" s="14">
+        <v>300</v>
+      </c>
+      <c r="C30" s="14">
+        <v>127</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
       <c r="E30" s="14">
         <v>35</v>
       </c>
@@ -2098,15 +2230,15 @@
         <v>4</v>
       </c>
       <c r="H30" s="14">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>362</v>
+        <v>862</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>1078</v>
+        <v>578</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>67</v>
@@ -2118,16 +2250,22 @@
         <v>59</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
         <v>46281</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
+      <c r="B31" s="14">
+        <v>300</v>
+      </c>
+      <c r="C31" s="14">
+        <v>190</v>
+      </c>
+      <c r="D31" s="14">
+        <v>15</v>
+      </c>
       <c r="E31" s="14">
         <v>40</v>
       </c>
@@ -2138,15 +2276,15 @@
         <v>4</v>
       </c>
       <c r="H31" s="14">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>430</v>
+        <v>810</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>1010</v>
+        <v>630</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>65</v>
@@ -2165,28 +2303,34 @@
       <c r="A32" s="13">
         <v>46282</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>193</v>
+      </c>
+      <c r="D32" s="14">
+        <v>45</v>
+      </c>
       <c r="E32" s="14">
         <v>60</v>
       </c>
       <c r="F32" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G32" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H32" s="14">
-        <v>193</v>
+        <v>30</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>603</v>
+        <v>1048</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>837</v>
+        <v>392</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>57</v>
@@ -2198,52 +2342,100 @@
         <v>57</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B33" s="14">
+        <v>300</v>
+      </c>
+      <c r="C33" s="14">
+        <v>98</v>
+      </c>
+      <c r="D33" s="14">
+        <v>60</v>
+      </c>
+      <c r="E33" s="14">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
+        <v>350</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>868</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>572</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B34" s="14">
+        <v>360</v>
+      </c>
+      <c r="C34" s="14">
+        <v>66</v>
+      </c>
+      <c r="D34" s="14">
+        <v>60</v>
+      </c>
+      <c r="E34" s="14">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>180</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>786</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>654</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>

--- a/12626455.xlsx
+++ b/12626455.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A469DF-7521-40B9-A340-4E8CE49E0DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315709C0-C7E9-41FF-995D-7F3403555EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>Ca was there and Saturday ruined</t>
+  </si>
+  <si>
+    <t>okay day</t>
   </si>
 </sst>
 </file>
@@ -2438,26 +2441,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B35" s="14">
+        <v>180</v>
+      </c>
+      <c r="C35" s="14">
+        <v>203</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>120</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>533</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>907</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>

--- a/12626455.xlsx
+++ b/12626455.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43740B6-DAB0-44B0-A883-8D40BC456C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460E6B67-ACF5-4733-8623-F84EED60CF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2729,26 +2729,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+      <c r="A41" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="9">
+        <v>240</v>
+      </c>
+      <c r="C41" s="9">
+        <v>187</v>
+      </c>
+      <c r="D41" s="9">
+        <v>30</v>
+      </c>
+      <c r="E41" s="9">
+        <v>30</v>
+      </c>
+      <c r="F41" s="9">
+        <v>200</v>
+      </c>
+      <c r="G41" s="9">
+        <v>4</v>
+      </c>
+      <c r="H41" s="9">
+        <v>100</v>
+      </c>
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
+        <v>787</v>
+      </c>
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
+        <v>653</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="8"/>
